--- a/content/october-2026-system/calendar/calendar.xlsx
+++ b/content/october-2026-system/calendar/calendar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -424,23 +424,27 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="49" customWidth="1" min="20" max="20"/>
-    <col width="43" customWidth="1" min="21" max="21"/>
-    <col width="33" customWidth="1" min="22" max="22"/>
-    <col width="31" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
-    <col width="33" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="43" customWidth="1" min="23" max="23"/>
+    <col width="33" customWidth="1" min="24" max="24"/>
+    <col width="37" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="28" max="28"/>
+    <col width="46" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,48 +535,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>cta_a</t>
+          <t>cta_ig_ru</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>cta_b</t>
+          <t>cta_ig_en</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>course_objection</t>
+          <t>cta_tg</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cta_vk</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>course_touch</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>prep_needed</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>time_credits_estimate</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>main_metric</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>flexible_update_required</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>flex_what_to_check</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>flex_backup_topic</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -646,56 +672,72 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G01) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G01 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>Голосовая заметка + доступ к ChatGPT</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X2" t="b">
-        <v>0</v>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_готовится_в_этой_сессии</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -769,7 +811,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -779,46 +821,62 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G01) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G01 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -842,12 +900,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3 способа проверить ответ прежде чем использовать его</t>
+          <t>Проверить рабочий ответ ИИ тремя способами: открыть первоисточник, сверить конкретное утверждение, независимо проверить цифры</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Как поймать ChatGPT на вранье</t>
+          <t>Как проверить ответ ИИ, а не просто ещё раз переспросить</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -862,22 +920,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Как поймать ChatGPT на вранье за руку.</t>
+          <t>Ответ ИИ звучит уверенно. Уверенность — не доказательство.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ты почти отправил клиенту то, чего не проверил.</t>
+          <t>Три проверки: первоисточник, конкретное утверждение, цифры отдельно — а не 'переспросить ещё раз'.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Три проверки: переспросить с других слов, попросить источник/ход рассуждения, сверить с тем, что знаешь сам</t>
+          <t>Один и тот же ответ до проверки (выглядит убедительно) и после (часть цифр не подтвердилась)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Прогнать свой последний рабочий ответ ИИ через все три проверки</t>
+          <t>Прогнать свой последний рабочий ответ ИИ через все три проверки, не полагаясь на повторный вопрос модели</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -892,56 +950,72 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G01) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G01 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1015,7 +1089,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1025,46 +1099,62 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G02) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G02 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X5" t="b">
-        <v>0</v>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1138,56 +1228,72 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G02) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G02 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X6" t="b">
-        <v>0</v>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1221,7 +1327,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Карусель</t>
+          <t>Reels</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,56 +1367,72 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Карусель RU @neurumonk + Карусель EN @alov.lab · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G02) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G02 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>≈1 карусель-рендер (без HeyGen)</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>≈1 HeyGen-генерация + монтаж</t>
+        </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1384,56 +1506,72 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Мягкое упоминание: этот приём подробно на курсе</t>
+          <t>Полный материал (методичка G02) — пост+файл в t.me/AlovLab. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G02 в закрепе/первом комментарии. Статус: файл готов (workbook.pdf/.docx, guides/G0X-…/) — публикация в Telegram/VK на стороне человека, самой публикации ещё не было</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Этот навык — часть модуля «Земля Слов» курса «Нейросети и ChatGPT для каждого» (6 видеоуроков, 6 «Земель»). Для старта на курсе достаточно того уровня, что уже есть после этих 7 дней — специальных предпосылок сайт не заявляет (НЕТ ДАННЫХ на явные технические требования).</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1467,7 +1605,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Карусель</t>
+          <t>Reels</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1477,12 +1615,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Один кадр — цена фотосессии.</t>
+          <t>Один кадр вместо целой фотосессии.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>За эту картинку раньше платили фотографу и студии на полдня.</t>
+          <t>Не про замену фотографа — про то, что можно сделать без него, когда бюджета нет.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1507,56 +1645,80 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Карусель RU @neurumonk + Карусель EN @alov.lab · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G03) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G03 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>≈1 карусель-рендер (без HeyGen)</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X9" t="b">
-        <v>1</v>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>≈1 HeyGen-генерация + монтаж</t>
+        </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Какой именно инструмент генерации/улучшения изображений называем и его реальные возможности/лимиты на дату публикации — не заявлять цену/качество, которые не проверены.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Резерв: «Что реально можно поправить в слабом фото, а что нет» — тот же навык, честные границы возможностей, без сравнения с фотосессией и без привязки к конкретному инструменту.</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1630,56 +1792,72 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G03) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G03 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X10" t="b">
-        <v>0</v>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1753,7 +1931,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1763,46 +1941,62 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G04) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G04 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X11" t="b">
-        <v>0</v>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1876,56 +2070,72 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G04) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G04 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X12" t="b">
-        <v>0</v>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1999,7 +2209,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2009,46 +2219,62 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G05) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G05 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X13" t="b">
-        <v>0</v>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2122,56 +2348,72 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G05) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G05 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X14" t="b">
-        <v>0</v>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2245,7 +2487,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2255,46 +2497,62 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Мягкое упоминание: этот приём подробно на курсе</t>
+          <t>Полный материал (методичка G05) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G05 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Модуль «Земля Изображений» на курсе разбирает это подробнее: пример задания и разбор результата (НЕТ ДАННЫХ на реальный пример ученика — используется учебный пример, явно помеченный как учебный, реальных без разрешения не публикуем).</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X15" t="b">
-        <v>0</v>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2343,7 +2601,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Одна запись. Любой нужный язык на выходе.</t>
+          <t>Одна запись. Дальше — перевод пайплайном, не актёром озвучки.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2368,56 +2626,80 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G06) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G06 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X16" t="b">
-        <v>1</v>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Точный список поддерживаемых языков и реальное качество синхронизации на используемой платформе — не заявлять число языков без проверки в актуальной документации платформы.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Резерв: «Разбор одного шага в пайплайне аватара, который чаще всего ломается» — та же тема, без заявлений о конкретном числе языков.</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2491,7 +2773,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2501,46 +2783,62 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G06) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G06 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X17" t="b">
-        <v>1</v>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2604,7 +2902,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Дальше — реклама за вечер, не за 150 тысяч</t>
+          <t>Дальше — что реально можно собрать за вечер в рекламе</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2614,56 +2912,72 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G06) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G06 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X18" t="b">
-        <v>0</v>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2687,12 +3001,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Разобрать, что реально можно/нельзя собрать за вечер в рекламном ролике с ИИ</t>
+          <t>Честно разобрать, что реально можно собрать за вечер в простом рекламном ролике с ИИ, а что всё ещё требует студии — без сравнения с ценой агентства</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Реклама за вечер, а не за 150 тысяч</t>
+          <t>Реклама за вечер. Но не любая</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2707,22 +3021,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>За этот ролик агентство выставило бы счёт на 150 тысяч.</t>
+          <t>Реклама за вечер. Но не любая.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>У тебя нет команды из десяти человек. У тебя есть вечер.</t>
+          <t>Что ИИ берёт на себя сам, а что всё ещё нужно тебе — без придуманных цифр сравнения.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Честный пайплайн простого рекламного ролика + что не заменит агентство</t>
+          <t>Честный пайплайн простого рекламного ролика + явная граница, что не заменит студию</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Собрать свой план простого рекламного ролика на вечер</t>
+          <t>Собрать свой план простого рекламного ролика на вечер, зная границы</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2737,7 +3051,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2747,46 +3061,70 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G07) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G07 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X19" t="b">
-        <v>1</v>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Не допустить непроверенное сравнение с ценой агентства/продакшна — таких данных нет, сравнение по цене в материал не включать вообще.</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Резерв: «Что ИИ берёт на себя в рекламном ролике, а что всё ещё нужно снимать» — тот же честный разбор границ без каких-либо цифр сравнения.</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2860,56 +3198,80 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G07) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G07 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X20" t="b">
-        <v>1</v>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Доступность и реальные возможности конкретного инструмента AI-подкастинга на дату публикации — быстро меняющийся рынок инструментов.</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Резерв: «Как звучит один и тот же текст двумя разными ИИ-голосами» — сравнение без привязки к конкретному непроверенному инструменту-платформе.</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2983,7 +3345,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2993,46 +3355,62 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G07) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G07 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X21" t="b">
-        <v>0</v>
-      </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3106,56 +3484,72 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Мягкое упоминание: этот приём подробно на курсе</t>
+          <t>Полный материал (методичка G07) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G07 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Модули «Земля Видео», «Звук», «Аватары» на курсе. Как устроена поддержка: закрытый Telegram-канал + ИИ-ассистент по курсу на всех тарифах (подтверждено CLAUDE.md); личное менторство — только тариф ПРО. Старт с нуля, явных предпосылок сайт не заявляет.</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3189,7 +3583,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Карусель</t>
+          <t>Reels</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3229,56 +3623,72 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Карусель RU @neurumonk + Карусель EN @alov.lab · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G08) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G08 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>≈1 карусель-рендер (без HeyGen)</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X23" t="b">
-        <v>0</v>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>≈1 HeyGen-генерация + монтаж</t>
+        </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3352,56 +3762,80 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G08) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G08 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X24" t="b">
-        <v>1</v>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Доступность и условия конкретной платформы для сборки личного агента на дату публикации.</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Резерв: «Один агент, одна задача: что он умеет прямо сейчас» — то же самое, но без привязки к конкретной непроверенной платформе, обобщённый показ принципа.</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3475,7 +3909,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3485,46 +3919,70 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G08) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G08 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X25" t="b">
-        <v>1</v>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>MCP — активно развивающийся протокол (последняя известная проектная спецификация — 28.07.2026, см. content/reels/2026-09-29/sources.json). Проверить, не вышло ли обновление к дате публикации.</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Резерв: «Как агент вообще выбирает, какой инструмент открыть» — общий принцип без привязки к номеру версии протокола.</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3548,7 +4006,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Показать честную схему навык → продукт → клиент → деньги</t>
+          <t>Показать честную схему навык → продукт → клиент → деньги, ответить на вопрос «кому подходит курс»</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3563,7 +4021,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GROWTH</t>
+          <t>AUTHORITY (курс-точка)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3598,56 +4056,72 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G09) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G09 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Кому подходит курс (по сайту): не только новичкам — тем, кто хочет систему вместо разрозненных приёмов. Явных требований по стартовому уровню сайт не формулирует (НЕТ ДАННЫХ на точные пороги).</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X26" t="b">
-        <v>0</v>
-      </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3721,7 +4195,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3731,46 +4205,62 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G09) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G09 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X27" t="b">
-        <v>0</v>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3844,56 +4334,72 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G09) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G09 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X28" t="b">
-        <v>0</v>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3917,7 +4423,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Написать и подготовить к отправке реальный оффер под одну из услуг</t>
+          <t>Написать оффер под одну из услуг, готовый к отправке — без обещания, что заказ придёт</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3937,12 +4443,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Первый клиент — не через полгода. Через неделю.</t>
+          <t>Первый оффер, который можно отправить сегодня.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Оффер не обязан быть идеальным. Он обязан быть отправлен.</t>
+          <t>Готовый оффер — не гарантия клиента. Но без него клиента точно не будет.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3952,7 +4458,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Написать свой оффер и знать, кому его первому отправить</t>
+          <t>Написать свой оффер и знать, кому его первому отправить — результат этого дня - готовый оффер, не заказ</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3967,7 +4473,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3977,46 +4483,62 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Мягкое упоминание: этот приём подробно на курсе</t>
+          <t>Полный материал (методичка G09) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G09 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Чем платное обучение дополняет бесплатные методички месяца: методички — отдельные приёмы по запросу; курс — система по 6 направлениям (Слова/Изображения/Видео/Звук/Аватары/Знания) + на тарифе ПРО проверка заданий и личное менторство (подтверждено CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X29" t="b">
-        <v>0</v>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4090,56 +4612,72 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Reels RU @neurumonk + Reels EN @alov.lab + Shorts YouTube · Telegram-пост+методичка · VK-пост</t>
+          <t>Reels RU @neurumonk + Reels EN @alov.lab + YouTube Shorts-адаптация + VK Клип · Telegram-пост+методичка · VK-пост</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Без прямого упоминания курса</t>
+          <t>Полный материал (методичка G10) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>VK Клип + контекстный пост в vk.com/alovlab, ссылка на методичку G10 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>≈1 HeyGen-генерация + монтаж</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Досмотр/сохранения/подписки</t>
-        </is>
-      </c>
-      <c r="X30" t="b">
-        <v>0</v>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Досмотр 72ч + сохранения + подписки</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4213,7 +4751,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>уточняется в реестре методичек</t>
+          <t>см. guides/00-registry.md</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4223,40 +4761,54 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Сохранить/сохранить методичку в Telegram (без ссылки в IG, действие внутри площадки)</t>
+          <t>Сохрани пост / ответь ключевым словом в комментариях — ссылок в IG нет весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Переход по ссылке в методичку/курс (только после подтверждённого снятия ограничения IG)</t>
+          <t>Save the post / reply with a keyword в комментариях — no links in IG весь месяц (ограничение до 30.10.2026, см. sources/00-verification-log.md)</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Мягкое упоминание: этот приём подробно на курсе</t>
+          <t>Полный материал (методичка G10) — пост+файл в t.me/AlovLab. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>Контекстный пост в vk.com/alovlab, ссылка на методичку G10 в закрепе/первом комментарии. Статус: место выдачи не подготовлено — файл методички ещё не написан</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Прямое честное предложение курса «Нейросети и ChatGPT для каждого»: 6 видеоуроков/6 «Земель», 3 тарифа (МИНИ/БАЗОВЫЙ/ПРО — цены на октябрь НЕ переподтверждены вживую, см. sources/00-verification-log.md, не называть цифры до проверки), гарантия возврата 14 дней (подтверждено CLAUDE.md). EN-версия курса не подтверждена — для @alov.lab CTA ведёт на содержательное действие, не на покупку.</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>Реальный рабочий пример из своей практики</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>≈1 карусель-рендер (без HeyGen)</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Сохранения/пересылки/подписки</t>
-        </is>
-      </c>
-      <c r="X31" t="b">
-        <v>0</v>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>запланирован</t>
+          <t>Сохранения + пересылки + подписки</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>структура_есть_текст_не_написан</t>
         </is>
       </c>
     </row>

--- a/content/october-2026-system/calendar/calendar.xlsx
+++ b/content/october-2026-system/calendar/calendar.xlsx
@@ -444,7 +444,7 @@
     <col width="26" customWidth="1" min="26" max="26"/>
     <col width="60" customWidth="1" min="27" max="27"/>
     <col width="60" customWidth="1" min="28" max="28"/>
-    <col width="46" customWidth="1" min="29" max="29"/>
+    <col width="58" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,10 +595,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -720,24 +718,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z2" t="b">
+        <v>0</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>структура_есть_текст_готовится_в_этой_сессии</t>
+          <t>текст_написан_согласовать_с_существующим_heygen_проектом</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -859,24 +853,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z3" t="b">
+        <v>0</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>текст_написан_RU_EN_готов_к_экспорту</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -998,24 +988,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z4" t="b">
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>текст_написан_RU_EN_готов_к_экспорту</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1137,24 +1123,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z5" t="b">
+        <v>0</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>текст_написан_RU_EN_готов_к_экспорту</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1276,24 +1258,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z6" t="b">
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>текст_написан_RU_EN_готов_к_экспорту</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1415,24 +1393,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z7" t="b">
+        <v>0</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>текст_написан_RU_EN_готов_к_экспорту</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1554,24 +1528,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z8" t="b">
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>текст_написан_RU_EN_готов_к_экспорту</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1693,10 +1663,8 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="Z9" t="b">
+        <v>1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1710,15 +1678,13 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1840,24 +1806,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z10" t="b">
+        <v>0</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1979,24 +1941,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z11" t="b">
+        <v>0</v>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2118,24 +2076,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z12" t="b">
+        <v>0</v>
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2257,24 +2211,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z13" t="b">
+        <v>0</v>
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2396,24 +2346,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z14" t="b">
+        <v>0</v>
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2535,24 +2481,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z15" t="b">
+        <v>0</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2674,10 +2616,8 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="Z16" t="b">
+        <v>1</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2691,15 +2631,13 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2821,24 +2759,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z17" t="b">
+        <v>0</v>
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2960,24 +2894,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z18" t="b">
+        <v>0</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3099,10 +3029,8 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="Z19" t="b">
+        <v>1</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3116,15 +3044,13 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3246,10 +3172,8 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="Z20" t="b">
+        <v>1</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3263,15 +3187,13 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3393,24 +3315,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z21" t="b">
+        <v>0</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3532,24 +3450,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z22" t="b">
+        <v>0</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3671,24 +3585,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z23" t="b">
+        <v>0</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3810,10 +3720,8 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="Z24" t="b">
+        <v>1</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3827,15 +3735,13 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3957,10 +3863,8 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="Z25" t="b">
+        <v>1</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3974,15 +3878,13 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4104,24 +4006,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z26" t="b">
+        <v>0</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4243,24 +4141,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z27" t="b">
+        <v>0</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A28" t="n">
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4382,24 +4276,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z28" t="b">
+        <v>0</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A29" t="n">
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4521,24 +4411,20 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z29" t="b">
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A30" t="n">
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4660,24 +4546,20 @@
           <t>Досмотр 72ч + сохранения + подписки</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z30" t="b">
+        <v>0</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" t="n">
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4799,16 +4681,14 @@
           <t>Сохранения + пересылки + подписки</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="Z31" t="b">
+        <v>0</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>структура_есть_текст_не_написан</t>
+          <t>запланирован_текст_не_написан</t>
         </is>
       </c>
     </row>
